--- a/교재/엑셀교재v2/027_목표값찾기_실습.xlsx
+++ b/교재/엑셀교재v2/027_목표값찾기_실습.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FORYOUCOM\Documents\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D874C47C-128C-4523-9545-B13B154B05F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2634AF-F442-4924-A8A4-12D3A5BF9F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용안내" sheetId="1" r:id="rId1"/>
@@ -23,24 +23,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">사용안내!$A$1:$D$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
   <si>
     <t>027 목표값 찾기 사용 안내</t>
   </si>
@@ -166,6 +153,10 @@
   </si>
   <si>
     <t>수식 셀 G12에는 =SUM(G4:G11)이 들어 있습니다. 목표를 맞출 계산 결과 셀입니다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>‘판매현황’표에서 손실금액 합계[G12]가 2,000,000이 되려면 불량률[G14]이 얼마가 되어야 하는지 ‘목표값 찾기’ 기능을 이용하여 계산하시오.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -263,11 +254,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -506,12 +497,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" ht="36" customHeight="1">
       <c r="A2" s="1"/>
@@ -520,148 +511,148 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4" ht="36" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
     </row>
     <row r="5" spans="1:4" ht="36" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" ht="36" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
     </row>
     <row r="7" spans="1:4" ht="36" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" ht="36" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:4" ht="36" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
     </row>
     <row r="10" spans="1:4" ht="36" customHeight="1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
     </row>
     <row r="11" spans="1:4" ht="36" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
     </row>
     <row r="12" spans="1:4" ht="36" customHeight="1">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="13" spans="1:4" ht="36" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
     </row>
     <row r="14" spans="1:4" ht="36" customHeight="1">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="36" customHeight="1">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:4" ht="36" customHeight="1">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" ht="36" customHeight="1">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" spans="1:4" ht="36" customHeight="1">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="36" customHeight="1">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" spans="1:4" ht="36" customHeight="1">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4" ht="36" customHeight="1">
       <c r="A21" s="1"/>
@@ -671,16 +662,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A19:D19"/>
@@ -690,6 +671,16 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1017,7 +1008,7 @@
     <row r="16" spans="1:9" ht="30" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
